--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:54</t>
+    <t xml:space="preserve">2026-09-09 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:42</t>
+    <t xml:space="preserve">2026-09-18 10:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:05</t>
+    <t xml:space="preserve">2026-09-23 12:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:10</t>
+    <t xml:space="preserve">2026-10-02 13:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Tomé</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Bárbara</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:37</t>
+    <t xml:space="preserve">2026-10-04 08:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:28</t>
+    <t xml:space="preserve">2026-10-05 09:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
